--- a/data/trans_orig/P36BPD10_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD10_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de raciones pescado o mariscos que consumen a la semana en 2023</t>
+          <t>Población según el número de raciones pescado o mariscos que consumen a la semana en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32333</t>
+          <t>31683</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>76745</t>
+          <t>76958</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21652</t>
+          <t>21985</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>56199</t>
+          <t>54577</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>58257</t>
+          <t>62880</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>115975</t>
+          <t>116260</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,3%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>153792</t>
+          <t>151707</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>225394</t>
+          <t>222003</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>55,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>121954</t>
+          <t>121644</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>168007</t>
+          <t>168913</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,64%</t>
+          <t>53,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>290247</t>
+          <t>296589</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>372391</t>
+          <t>377804</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>52,97%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>124996</t>
+          <t>125792</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>196442</t>
+          <t>198596</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>109880</t>
+          <t>109493</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>156581</t>
+          <t>156415</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>253813</t>
+          <t>250935</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>334727</t>
+          <t>332557</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>46,63%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>37902</t>
+          <t>37010</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>73116</t>
+          <t>75910</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>25500</t>
+          <t>25972</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>60952</t>
+          <t>59313</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>68888</t>
+          <t>70600</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>121948</t>
+          <t>122296</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,1%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>189566</t>
+          <t>188842</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>243030</t>
+          <t>241898</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>57,34%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>241731</t>
+          <t>241705</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>369804</t>
+          <t>373600</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>47,25%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>454488</t>
+          <t>450134</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>602472</t>
+          <t>609736</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>48,23%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>65,33%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>129424</t>
+          <t>127315</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>181017</t>
+          <t>180793</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>115213</t>
+          <t>108955</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>218693</t>
+          <t>219271</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>251522</t>
+          <t>254399</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>377652</t>
+          <t>380038</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,72%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>41564</t>
+          <t>41048</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>69967</t>
+          <t>70658</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>44065</t>
+          <t>43511</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>66841</t>
+          <t>66487</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>91003</t>
+          <t>90588</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>128197</t>
+          <t>128938</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,95%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>236622</t>
+          <t>234950</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>284109</t>
+          <t>282511</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>52,97%</t>
+          <t>52,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>229775</t>
+          <t>231493</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>268234</t>
+          <t>268134</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>479990</t>
+          <t>477608</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>544018</t>
+          <t>540270</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>44,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>50,08%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>196821</t>
+          <t>198881</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>243728</t>
+          <t>245859</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>218404</t>
+          <t>219754</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>257910</t>
+          <t>257325</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>47,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>430483</t>
+          <t>433352</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>489746</t>
+          <t>492278</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>45,63%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28808</t>
+          <t>33210</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>114681</t>
+          <t>110847</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>45403</t>
+          <t>45886</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>71037</t>
+          <t>71168</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>78187</t>
+          <t>85173</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>168245</t>
+          <t>167016</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,44%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>381120</t>
+          <t>385790</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>730154</t>
+          <t>739912</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>245679</t>
+          <t>242941</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>316351</t>
+          <t>318581</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>44,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>669386</t>
+          <t>663965</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1134461</t>
+          <t>1090569</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>68,19%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>121389</t>
+          <t>118437</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>402090</t>
+          <t>401560</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>45,28%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>334699</t>
+          <t>336093</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>415704</t>
+          <t>427013</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>59,93%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>386940</t>
+          <t>418168</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>777186</t>
+          <t>779263</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>48,72%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>37367</t>
+          <t>37680</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>64553</t>
+          <t>64854</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>31120</t>
+          <t>32050</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>50469</t>
+          <t>50060</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>76351</t>
+          <t>74678</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>108217</t>
+          <t>107818</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>239381</t>
+          <t>238232</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>281423</t>
+          <t>282075</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>212985</t>
+          <t>213066</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>248771</t>
+          <t>247053</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>463959</t>
+          <t>462981</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>518922</t>
+          <t>519156</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>46,91%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>228389</t>
+          <t>227784</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>271976</t>
+          <t>271221</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>258652</t>
+          <t>258824</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>295209</t>
+          <t>293902</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>47,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>497688</t>
+          <t>497299</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>552975</t>
+          <t>555022</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>50,15%</t>
         </is>
       </c>
     </row>
@@ -3010,12 +3010,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>19575</t>
+          <t>19867</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>36402</t>
+          <t>36524</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10826</t>
+          <t>11704</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>48369</t>
+          <t>49138</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>26735</t>
+          <t>30005</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>78213</t>
+          <t>77761</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3123,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>136877</t>
+          <t>136803</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>166775</t>
+          <t>168541</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3138,12 +3138,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>72653</t>
+          <t>81706</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>270783</t>
+          <t>270263</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3173,12 +3173,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>154547</t>
+          <t>166491</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>421644</t>
+          <t>420154</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>43,09%</t>
         </is>
       </c>
     </row>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>172839</t>
+          <t>171073</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>202438</t>
+          <t>202537</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>46,65%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>55,23%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>293935</t>
+          <t>292420</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>523091</t>
+          <t>514842</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>480628</t>
+          <t>481812</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>790393</t>
+          <t>780788</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>80,07%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>10335</t>
+          <t>10237</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>22741</t>
+          <t>22587</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>23405</t>
+          <t>24075</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>41045</t>
+          <t>39703</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>36535</t>
+          <t>37131</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>57168</t>
+          <t>57820</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>117068</t>
+          <t>117412</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>144445</t>
+          <t>142632</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>190200</t>
+          <t>188959</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>219427</t>
+          <t>216909</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>51,58%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>313768</t>
+          <t>314462</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>352782</t>
+          <t>354679</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>44,44%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>50,13%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>122764</t>
+          <t>123368</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>149759</t>
+          <t>149784</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>176687</t>
+          <t>177011</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>205110</t>
+          <t>205276</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>306985</t>
+          <t>304832</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>346400</t>
+          <t>345863</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>48,88%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>255736</t>
+          <t>264001</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>381948</t>
+          <t>383751</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>239610</t>
+          <t>235356</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>328744</t>
+          <t>329673</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>530840</t>
+          <t>536943</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>691546</t>
+          <t>695730</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,78%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1578156</t>
+          <t>1579914</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2107175</t>
+          <t>2170613</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>62,84%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1297094</t>
+          <t>1311584</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1714346</t>
+          <t>1720948</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>3060550</t>
+          <t>3022582</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>3689488</t>
+          <t>3725865</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>52,37%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1077680</t>
+          <t>1060345</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1518127</t>
+          <t>1516187</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1645345</t>
+          <t>1638491</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2136723</t>
+          <t>2096734</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>57,29%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2892755</t>
+          <t>2869289</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3495261</t>
+          <t>3526907</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>49,58%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD10_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD10_2023-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>52041</t>
+          <t>54290</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31683</t>
+          <t>34957</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>76958</t>
+          <t>78796</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>35211</t>
+          <t>44707</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21985</t>
+          <t>28633</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>54577</t>
+          <t>66383</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>87251</t>
+          <t>98997</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>62880</t>
+          <t>73588</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>116260</t>
+          <t>129150</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,77%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>188626</t>
+          <t>200021</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>151707</t>
+          <t>168258</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>222003</t>
+          <t>234365</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>57,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>144826</t>
+          <t>163384</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>121644</t>
+          <t>138048</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>168913</t>
+          <t>188282</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>333452</t>
+          <t>363405</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>296589</t>
+          <t>324472</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>377804</t>
+          <t>405594</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>47,18%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,97%</t>
+          <t>52,65%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>159321</t>
+          <t>153482</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>125792</t>
+          <t>121280</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>198596</t>
+          <t>187204</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>133163</t>
+          <t>154421</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>109493</t>
+          <t>128884</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>156415</t>
+          <t>180420</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>49,77%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>292484</t>
+          <t>307903</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>250935</t>
+          <t>266820</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>332557</t>
+          <t>351318</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>45,61%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>54093</t>
+          <t>60303</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>37010</t>
+          <t>42436</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>75910</t>
+          <t>82536</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>43690</t>
+          <t>47813</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>25972</t>
+          <t>35372</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>59313</t>
+          <t>64267</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>97783</t>
+          <t>108116</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>70600</t>
+          <t>86083</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>122296</t>
+          <t>138682</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>14,2%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>215558</t>
+          <t>248252</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>188842</t>
+          <t>218802</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>241898</t>
+          <t>276324</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>46,03%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>58,12%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>286169</t>
+          <t>251915</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>241705</t>
+          <t>228682</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>373600</t>
+          <t>274862</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>50,27%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>54,85%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>501727</t>
+          <t>500167</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>450134</t>
+          <t>460466</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>609736</t>
+          <t>538253</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
+          <t>55,12%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>152230</t>
+          <t>166843</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>127315</t>
+          <t>142440</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>180793</t>
+          <t>194478</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>181645</t>
+          <t>201355</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>108955</t>
+          <t>178238</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>219271</t>
+          <t>224449</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>333875</t>
+          <t>368197</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>254399</t>
+          <t>330938</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>380038</t>
+          <t>406090</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>41,59%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>421882</t>
+          <t>475397</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>421882</t>
+          <t>475397</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>421882</t>
+          <t>475397</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>933386</t>
+          <t>976480</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>933386</t>
+          <t>976480</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>933386</t>
+          <t>976480</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>55038</t>
+          <t>66704</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>41048</t>
+          <t>51573</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>70658</t>
+          <t>86280</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>54209</t>
+          <t>65552</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>43511</t>
+          <t>52730</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>66487</t>
+          <t>79533</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>109247</t>
+          <t>132256</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>90588</t>
+          <t>111592</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>128938</t>
+          <t>153201</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,33%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>259000</t>
+          <t>299998</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>234950</t>
+          <t>274912</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>282511</t>
+          <t>327110</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,32 +1785,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>250092</t>
+          <t>285929</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>231493</t>
+          <t>264100</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>268134</t>
+          <t>305455</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>509091</t>
+          <t>585927</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>477608</t>
+          <t>552913</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>540270</t>
+          <t>621599</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>50,01%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>222300</t>
+          <t>254135</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>198881</t>
+          <t>228478</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>245859</t>
+          <t>280202</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>238168</t>
+          <t>270658</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>219754</t>
+          <t>251994</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>257325</t>
+          <t>292072</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>47,44%</t>
+          <t>46,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>460468</t>
+          <t>524793</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>433352</t>
+          <t>490386</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>492278</t>
+          <t>560128</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>45,06%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,102 +2093,102 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>73940</t>
+          <t>70843</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33210</t>
+          <t>55567</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>110847</t>
+          <t>88380</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>10,12%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>7,94%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>12,63%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>67518</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>54627</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>79628</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>9,17%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>7,42%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>10,81%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>138361</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>119781</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>160179</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>9,63%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>8,34%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3,74%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>12,5%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>58437</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>45886</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>71168</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>8,2%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>6,44%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>9,99%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>132377</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>85173</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>167016</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>8,28%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>5,33%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>11,15%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>531123</t>
+          <t>321757</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>385790</t>
+          <t>292522</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>739912</t>
+          <t>348271</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>49,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,67 +2241,67 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>292601</t>
+          <t>320426</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>242941</t>
+          <t>299992</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>318581</t>
+          <t>341853</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
+          <t>46,42%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>776</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>642183</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>610286</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>682592</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
           <t>44,71%</t>
         </is>
       </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>776</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>823723</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>663965</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>1090569</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>51,5%</t>
-        </is>
-      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>47,53%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>281846</t>
+          <t>307152</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>118437</t>
+          <t>281698</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>401560</t>
+          <t>336050</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>361460</t>
+          <t>348551</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>336093</t>
+          <t>328443</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>427013</t>
+          <t>370227</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>59,93%</t>
+          <t>50,27%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>643306</t>
+          <t>655703</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>418168</t>
+          <t>617015</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>779263</t>
+          <t>688049</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>45,65%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>47,91%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>886908</t>
+          <t>699752</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>886908</t>
+          <t>699752</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>886908</t>
+          <t>699752</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1599406</t>
+          <t>1436247</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1599406</t>
+          <t>1436247</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1599406</t>
+          <t>1436247</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>50269</t>
+          <t>51688</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>37680</t>
+          <t>39028</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>64854</t>
+          <t>66473</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>40013</t>
+          <t>46604</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>32050</t>
+          <t>37167</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>50060</t>
+          <t>57744</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>90281</t>
+          <t>98291</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>74678</t>
+          <t>82623</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>107818</t>
+          <t>115065</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -2662,32 +2662,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>260215</t>
+          <t>286793</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>238232</t>
+          <t>261569</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>282075</t>
+          <t>311860</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>51,27%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>229807</t>
+          <t>259600</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>213066</t>
+          <t>242005</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>247053</t>
+          <t>277616</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>490022</t>
+          <t>546393</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>462981</t>
+          <t>518061</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>519156</t>
+          <t>578185</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>42,62%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>47,56%</t>
         </is>
       </c>
     </row>
@@ -2775,32 +2775,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>249721</t>
+          <t>269784</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>227784</t>
+          <t>246857</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>271221</t>
+          <t>295541</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,32 +2810,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>276778</t>
+          <t>301204</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>258824</t>
+          <t>282642</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>293902</t>
+          <t>319221</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>49,59%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>46,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>52,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>526499</t>
+          <t>570988</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>497299</t>
+          <t>540374</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>555022</t>
+          <t>601987</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>44,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>49,52%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>560204</t>
+          <t>608265</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>560204</t>
+          <t>608265</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>560204</t>
+          <t>608265</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>546598</t>
+          <t>607407</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>546598</t>
+          <t>607407</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>546598</t>
+          <t>607407</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1106802</t>
+          <t>1215672</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1106802</t>
+          <t>1215672</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1106802</t>
+          <t>1215672</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3005,32 +3005,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>27545</t>
+          <t>31911</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>19867</t>
+          <t>23447</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>36524</t>
+          <t>41564</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,32 +3040,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>29590</t>
+          <t>32193</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11704</t>
+          <t>24638</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>49138</t>
+          <t>41372</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,32 +3075,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>57135</t>
+          <t>64103</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>30005</t>
+          <t>52975</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>77761</t>
+          <t>77143</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>9,13%</t>
         </is>
       </c>
     </row>
@@ -3118,32 +3118,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>151764</t>
+          <t>166236</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>136803</t>
+          <t>150089</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>168541</t>
+          <t>181018</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,32 +3153,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>175032</t>
+          <t>191520</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>81706</t>
+          <t>176755</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>270263</t>
+          <t>206339</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,32 +3188,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>326796</t>
+          <t>357757</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>166491</t>
+          <t>336162</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>420154</t>
+          <t>381322</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>42,35%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>45,14%</t>
         </is>
       </c>
     </row>
@@ -3231,32 +3231,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>187416</t>
+          <t>207354</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>171073</t>
+          <t>192147</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>202537</t>
+          <t>225796</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>51,14%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>47,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>55,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,32 +3266,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>403746</t>
+          <t>215453</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>292420</t>
+          <t>200975</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>514842</t>
+          <t>230441</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>52,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,32 +3301,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>591161</t>
+          <t>422807</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>481812</t>
+          <t>400597</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>780788</t>
+          <t>445390</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>52,73%</t>
         </is>
       </c>
     </row>
@@ -3344,17 +3344,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>366724</t>
+          <t>405500</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>366724</t>
+          <t>405500</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>366724</t>
+          <t>405500</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3379,17 +3379,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>975092</t>
+          <t>844667</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>975092</t>
+          <t>844667</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>975092</t>
+          <t>844667</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3461,32 +3461,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>15689</t>
+          <t>18900</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>10237</t>
+          <t>13142</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>22587</t>
+          <t>27843</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,32 +3496,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>31047</t>
+          <t>33732</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>24075</t>
+          <t>26023</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>39703</t>
+          <t>43863</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,32 +3531,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>46736</t>
+          <t>52631</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>37131</t>
+          <t>42188</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>57820</t>
+          <t>65010</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,4%</t>
         </is>
       </c>
     </row>
@@ -3574,27 +3574,27 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>130222</t>
+          <t>141380</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>117412</t>
+          <t>126163</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>142632</t>
+          <t>156450</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>46,15%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3609,32 +3609,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>204340</t>
+          <t>225193</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>188959</t>
+          <t>209933</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>216909</t>
+          <t>242166</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>48,51%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,32 +3644,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>334562</t>
+          <t>366573</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>314462</t>
+          <t>345763</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>354679</t>
+          <t>389892</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>50,39%</t>
         </is>
       </c>
     </row>
@@ -3687,32 +3687,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>136251</t>
+          <t>149219</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>123368</t>
+          <t>133503</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>149784</t>
+          <t>162709</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,32 +3722,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>190033</t>
+          <t>205268</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>177011</t>
+          <t>188549</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>205276</t>
+          <t>220575</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,32 +3757,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>326284</t>
+          <t>354487</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>304832</t>
+          <t>332113</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>345863</t>
+          <t>374511</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>48,41%</t>
         </is>
       </c>
     </row>
@@ -3800,17 +3800,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>282162</t>
+          <t>309498</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>282162</t>
+          <t>309498</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>282162</t>
+          <t>309498</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3835,17 +3835,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>425420</t>
+          <t>464193</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>425420</t>
+          <t>464193</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>425420</t>
+          <t>464193</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>707582</t>
+          <t>773691</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>707582</t>
+          <t>773691</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>707582</t>
+          <t>773691</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3917,32 +3917,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>328614</t>
+          <t>354638</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>264001</t>
+          <t>314782</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>383751</t>
+          <t>398559</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,32 +3952,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>292197</t>
+          <t>338119</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>235356</t>
+          <t>307751</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>329673</t>
+          <t>371825</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,32 +3987,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>620811</t>
+          <t>692756</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>536943</t>
+          <t>639373</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>695730</t>
+          <t>748690</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>10,31%</t>
         </is>
       </c>
     </row>
@@ -4030,32 +4030,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1736507</t>
+          <t>1664437</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1579914</t>
+          <t>1601546</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2170613</t>
+          <t>1729154</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>45,41%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4065,32 +4065,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>1582867</t>
+          <t>1697968</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1311584</t>
+          <t>1647252</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1720948</t>
+          <t>1756622</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4100,32 +4100,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>3319374</t>
+          <t>3362404</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>3022582</t>
+          <t>3275951</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>3725865</t>
+          <t>3450220</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>47,52%</t>
         </is>
       </c>
     </row>
@@ -4143,32 +4143,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>1389084</t>
+          <t>1507968</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1060345</t>
+          <t>1440062</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1516187</t>
+          <t>1570302</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4178,32 +4178,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>1784993</t>
+          <t>1696910</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1638491</t>
+          <t>1644444</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2096734</t>
+          <t>1748824</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4213,32 +4213,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>3174077</t>
+          <t>3204877</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2869289</t>
+          <t>3112574</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3526907</t>
+          <t>3284075</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>45,23%</t>
         </is>
       </c>
     </row>
@@ -4256,17 +4256,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>3454205</t>
+          <t>3527042</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3454205</t>
+          <t>3527042</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3454205</t>
+          <t>3527042</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4291,17 +4291,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>3660057</t>
+          <t>3732996</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3660057</t>
+          <t>3732996</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3660057</t>
+          <t>3732996</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4326,17 +4326,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>7114262</t>
+          <t>7260038</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>7114262</t>
+          <t>7260038</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>7114262</t>
+          <t>7260038</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
